--- a/docs/alliance-templates/alliance-experts.xlsx
+++ b/docs/alliance-templates/alliance-experts.xlsx
@@ -7,25 +7,19 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="专家资源" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'专家资源'!$A$2:$F$2</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Sheet1'!$A$1:$F$6</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>填写说明：
-* 必填列。
-头衔 / 职位 / 行业 / 城市：文本，选填
-简介：文本，选填</t>
-  </si>
-  <si>
-    <t>姓名 *</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <si>
+    <t>姓名</t>
   </si>
   <si>
     <t>头衔</t>
@@ -41,13 +35,103 @@
   </si>
   <si>
     <t>简介</t>
+  </si>
+  <si>
+    <t>刘建国</t>
+  </si>
+  <si>
+    <t>教授/博导</t>
+  </si>
+  <si>
+    <t>人工智能研究院院长</t>
+  </si>
+  <si>
+    <t>人工智能</t>
+  </si>
+  <si>
+    <t>北京</t>
+  </si>
+  <si>
+    <t>从事人工智能与机器学习研究20年，发表SCI论文80余篇</t>
+  </si>
+  <si>
+    <t>孙晓华</t>
+  </si>
+  <si>
+    <t>高级工程师</t>
+  </si>
+  <si>
+    <t>技术总监</t>
+  </si>
+  <si>
+    <t>新能源</t>
+  </si>
+  <si>
+    <t>上海</t>
+  </si>
+  <si>
+    <t>新能源汽车电池技术专家，拥有15项发明专利</t>
+  </si>
+  <si>
+    <t>赵明远</t>
+  </si>
+  <si>
+    <t>副教授</t>
+  </si>
+  <si>
+    <t>大数据中心主任</t>
+  </si>
+  <si>
+    <t>大数据</t>
+  </si>
+  <si>
+    <t>广州</t>
+  </si>
+  <si>
+    <t>大数据分析与可视化方向研究，主持国家级项目3项</t>
+  </si>
+  <si>
+    <t>周丽萍</t>
+  </si>
+  <si>
+    <t>高级架构师</t>
+  </si>
+  <si>
+    <t>研发副总裁</t>
+  </si>
+  <si>
+    <t>互联网</t>
+  </si>
+  <si>
+    <t>深圳</t>
+  </si>
+  <si>
+    <t>互联网分布式系统架构设计专家，曾任多家企业技术顾问</t>
+  </si>
+  <si>
+    <t>吴建国</t>
+  </si>
+  <si>
+    <t>教授级高工</t>
+  </si>
+  <si>
+    <t>CTO</t>
+  </si>
+  <si>
+    <t>智能制造</t>
+  </si>
+  <si>
+    <t>杭州</t>
+  </si>
+  <si>
+    <t>工业互联网与智能制造领域资深专家，参与国家标准制定</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,14 +141,8 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
       <sz val="11"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -76,7 +154,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,34 +166,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -382,52 +444,141 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="true"/>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20"/>
-    <col customWidth="true" max="3" min="2" width="22"/>
-    <col customWidth="true" max="4" min="4" width="20"/>
-    <col customWidth="true" max="5" min="5" width="18"/>
-    <col customWidth="true" max="6" min="6" width="48"/>
+    <col customWidth="true" max="1" min="1" width="12"/>
+    <col customWidth="true" max="2" min="2" width="16"/>
+    <col customWidth="true" max="3" min="3" width="20"/>
+    <col customWidth="true" max="4" min="4" width="18"/>
+    <col customWidth="true" max="5" min="5" width="10"/>
+    <col customWidth="true" max="6" min="6" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" ht="80" customHeight="true">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="24" customHeight="true">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="true">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="2" ht="20" customHeight="true">
+      <c r="A2" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="true">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$2:$F$2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
+  <autoFilter ref="$A$1:$F$6"/>
 </worksheet>
 </file>
--- a/docs/alliance-templates/alliance-experts.xlsx
+++ b/docs/alliance-templates/alliance-experts.xlsx
@@ -1,137 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="专家资源" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Sheet1'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'专家资源'!$A$2:$F$2</definedName>
   </definedNames>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="122211" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
-  <si>
-    <t>姓名</t>
-  </si>
-  <si>
-    <t>头衔</t>
-  </si>
-  <si>
-    <t>职位</t>
-  </si>
-  <si>
-    <t>行业</t>
-  </si>
-  <si>
-    <t>城市</t>
-  </si>
-  <si>
-    <t>简介</t>
-  </si>
-  <si>
-    <t>刘建国</t>
-  </si>
-  <si>
-    <t>教授/博导</t>
-  </si>
-  <si>
-    <t>人工智能研究院院长</t>
-  </si>
-  <si>
-    <t>人工智能</t>
-  </si>
-  <si>
-    <t>北京</t>
-  </si>
-  <si>
-    <t>从事人工智能与机器学习研究20年，发表SCI论文80余篇</t>
-  </si>
-  <si>
-    <t>孙晓华</t>
-  </si>
-  <si>
-    <t>高级工程师</t>
-  </si>
-  <si>
-    <t>技术总监</t>
-  </si>
-  <si>
-    <t>新能源</t>
-  </si>
-  <si>
-    <t>上海</t>
-  </si>
-  <si>
-    <t>新能源汽车电池技术专家，拥有15项发明专利</t>
-  </si>
-  <si>
-    <t>赵明远</t>
-  </si>
-  <si>
-    <t>副教授</t>
-  </si>
-  <si>
-    <t>大数据中心主任</t>
-  </si>
-  <si>
-    <t>大数据</t>
-  </si>
-  <si>
-    <t>广州</t>
-  </si>
-  <si>
-    <t>大数据分析与可视化方向研究，主持国家级项目3项</t>
-  </si>
-  <si>
-    <t>周丽萍</t>
-  </si>
-  <si>
-    <t>高级架构师</t>
-  </si>
-  <si>
-    <t>研发副总裁</t>
-  </si>
-  <si>
-    <t>互联网</t>
-  </si>
-  <si>
-    <t>深圳</t>
-  </si>
-  <si>
-    <t>互联网分布式系统架构设计专家，曾任多家企业技术顾问</t>
-  </si>
-  <si>
-    <t>吴建国</t>
-  </si>
-  <si>
-    <t>教授级高工</t>
-  </si>
-  <si>
-    <t>CTO</t>
-  </si>
-  <si>
-    <t>智能制造</t>
-  </si>
-  <si>
-    <t>杭州</t>
-  </si>
-  <si>
-    <t>工业互联网与智能制造领域资深专家，参与国家标准制定</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -141,13 +28,23 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -157,8 +54,20 @@
         <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -167,24 +76,113 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -445,140 +443,234 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="true"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="12"/>
-    <col customWidth="true" max="2" min="2" width="16"/>
-    <col customWidth="true" max="3" min="3" width="20"/>
-    <col customWidth="true" max="4" min="4" width="18"/>
-    <col customWidth="true" max="5" min="5" width="10"/>
-    <col customWidth="true" max="6" min="6" width="50"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="true">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
+    <row r="1" ht="96" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>填写说明：
+* 必填列。
+头衔 / 职位 / 行业 / 城市：文本，选填
+简介：文本，选填</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
     </row>
-    <row r="2" ht="20" customHeight="true">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>姓名 *</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>头衔</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>职位</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>行业</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>简介</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="true">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>17</v>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>刘建国</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>教授/博导</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>人工智能研究院院长</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>人工智能</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>从事人工智能与机器学习研究20年，发表SCI论文80余篇</t>
+        </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="true">
-      <c r="A4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>23</v>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>孙晓华</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>高级工程师</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>技术总监</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>新能源汽车电池技术专家，拥有15项发明专利</t>
+        </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="true">
-      <c r="A5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>29</v>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>赵明远</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>大数据中心主任</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>大数据</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>大数据分析与可视化方向研究，主持国家级项目3项</t>
+        </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="true">
-      <c r="A6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>35</v>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>周丽萍</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>高级架构师</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>研发副总裁</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>互联网</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>互联网分布式系统架构设计专家，曾任多家企业技术顾问</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>吴建国</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>教授级高工</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>智能制造</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>工业互联网与智能制造领域资深专家，参与国家标准制定</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$F$6"/>
+  <autoFilter ref="A2:F2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>